--- a/Editing Excel cells/Set Cell Values/.NET/Set Cell Values/Set Cell Values/Data/Input.xlsx
+++ b/Editing Excel cells/Set Cell Values/.NET/Set Cell Values/Set Cell Values/Data/Input.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KarthikaSanthanaKris\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UG Branch\1041188-CreateXlsIOSamples\Editing Excel cells\Set Cell Values\.NET\Set Cell Values\Set Cell Values\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F6C97F9-17DC-4E79-8A81-2E5318CD33ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068F5AE1-4972-460C-AF0F-E9F9E7556DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{60BF4479-6214-42C8-B874-1617DC276577}"/>
   </bookViews>
@@ -39,24 +39,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t>Project Name</t>
+    <t>Product</t>
   </si>
   <si>
-    <t>Budget</t>
+    <t>Price</t>
   </si>
   <si>
-    <t>Start Date</t>
+    <t>Quantity</t>
   </si>
   <si>
-    <t>Alpha</t>
+    <t>Pen</t>
   </si>
   <si>
-    <t>Beta</t>
-  </si>
-  <si>
-    <t>Active</t>
+    <t>Notebook</t>
   </si>
 </sst>
 </file>
@@ -97,11 +94,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -437,56 +434,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E995BD-7CE1-41E2-AAF0-61D10DA8CAD9}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" customWidth="1"/>
-    <col min="2" max="2" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
+      <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>1000</v>
-      </c>
-      <c r="C2" s="3">
-        <v>46204</v>
-      </c>
-      <c r="D2" t="b">
-        <v>1</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C2" s="1">
+        <v>50</v>
+      </c>
+      <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1">
-        <v>2500</v>
-      </c>
-      <c r="C3" s="3">
-        <v>46208</v>
-      </c>
-      <c r="D3" t="b">
-        <v>0</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="C3" s="1">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>